--- a/base/base_limpa.xlsx
+++ b/base/base_limpa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:Q1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,33 +505,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26/11/2022</t>
+          <t>28/11/2022</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>11</v>
@@ -540,74 +540,74 @@
         <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28/11/2022</t>
+          <t>29/11/2022</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
         <v>25</v>
@@ -615,36 +615,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29/11/2022</t>
+          <t>30/11/2022</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
         <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
         <v>16</v>
@@ -653,16 +653,16 @@
         <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
         <v>25</v>
@@ -670,106 +670,106 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30/11/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
         <v>22</v>
@@ -780,164 +780,164 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
         <v>16</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>06/12/2022</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
         <v>19</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>24</v>
@@ -945,54 +945,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/12/2022</t>
+          <t>07/12/2022</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
         <v>24</v>
@@ -1000,103 +1000,103 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07/12/2022</t>
+          <t>08/12/2022</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
         <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
         <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08/12/2022</t>
+          <t>09/12/2022</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
         <v>22</v>
@@ -1110,18 +1110,18 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09/12/2022</t>
+          <t>10/12/2022</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
@@ -1136,28 +1136,28 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" t="n">
         <v>22</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
@@ -1165,88 +1165,88 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10/12/2022</t>
+          <t>12/12/2022</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/12/2022</t>
+          <t>13/12/2022</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
@@ -1270,20 +1270,20 @@
         <v>21</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13/12/2022</t>
+          <t>14/12/2022</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -1298,138 +1298,138 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
         <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14/12/2022</t>
+          <t>15/12/2022</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
         <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15/12/2022</t>
+          <t>16/12/2022</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
         <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P18" t="n">
         <v>23</v>
@@ -1440,36 +1440,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16/12/2022</t>
+          <t>17/12/2022</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
         <v>15</v>
@@ -1481,25 +1481,25 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
         <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17/12/2022</t>
+          <t>19/12/2022</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1509,217 +1509,217 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>21</v>
       </c>
       <c r="P20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19/12/2022</t>
+          <t>20/12/2022</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20/12/2022</t>
+          <t>21/12/2022</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21/12/2022</t>
+          <t>22/12/2022</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22/12/2022</t>
+          <t>23/12/2022</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1729,150 +1729,150 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23/12/2022</t>
+          <t>24/12/2022</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L25" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24/12/2022</t>
+          <t>26/12/2022</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
         <v>25</v>
@@ -1880,76 +1880,76 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26/12/2022</t>
+          <t>27/12/2022</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
         <v>8</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27/12/2022</t>
+          <t>28/12/2022</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
@@ -1958,56 +1958,56 @@
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O28" t="n">
         <v>22</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28/12/2022</t>
+          <t>29/12/2022</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>7</v>
@@ -2016,7 +2016,7 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
         <v>14</v>
@@ -2025,7 +2025,7 @@
         <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
         <v>19</v>
@@ -2037,7 +2037,7 @@
         <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="n">
         <v>25</v>
@@ -2045,51 +2045,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29/12/2022</t>
+          <t>30/12/2022</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
         <v>16</v>
       </c>
       <c r="L30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P30" t="n">
         <v>23</v>
@@ -2100,11 +2100,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30/12/2022</t>
+          <t>31/12/2022</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2114,34 +2114,34 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
         <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L31" t="n">
         <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O31" t="n">
         <v>21</v>
@@ -2150,29 +2150,29 @@
         <v>23</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31/12/2022</t>
+          <t>03/01/2023</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
         <v>9</v>
@@ -2181,99 +2181,99 @@
         <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03/01/2023</t>
+          <t>04/01/2023</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>05/01/2023</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
@@ -2291,28 +2291,28 @@
         <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K34" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L34" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q34" t="n">
         <v>25</v>
@@ -2320,24 +2320,24 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>05/01/2023</t>
+          <t>06/01/2023</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>8</v>
@@ -2352,22 +2352,22 @@
         <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q35" t="n">
         <v>25</v>
@@ -2375,11 +2375,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06/01/2023</t>
+          <t>07/01/2023</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2389,40 +2389,40 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O36" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P36" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="n">
         <v>25</v>
@@ -2430,11 +2430,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07/01/2023</t>
+          <t>09/01/2023</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2450,19 +2450,19 @@
         <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L37" t="n">
         <v>19</v>
@@ -2485,11 +2485,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09/01/2023</t>
+          <t>10/01/2023</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2502,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
         <v>10</v>
@@ -2520,16 +2520,16 @@
         <v>13</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N38" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P38" t="n">
         <v>24</v>
@@ -2540,51 +2540,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/01/2023</t>
+          <t>11/01/2023</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L39" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P39" t="n">
         <v>24</v>
@@ -2595,36 +2595,36 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/01/2023</t>
+          <t>12/01/2023</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
         <v>18</v>
@@ -2650,11 +2650,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12/01/2023</t>
+          <t>13/01/2023</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2664,52 +2664,52 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L41" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13/01/2023</t>
+          <t>14/01/2023</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2725,74 +2725,74 @@
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14/01/2023</t>
+          <t>16/01/2023</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L43" t="n">
         <v>17</v>
@@ -2801,13 +2801,13 @@
         <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q43" t="n">
         <v>25</v>
@@ -2815,15 +2815,15 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16/01/2023</t>
+          <t>17/01/2023</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>4</v>
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
         <v>13</v>
@@ -2859,35 +2859,35 @@
         <v>19</v>
       </c>
       <c r="O44" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P44" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17/01/2023</t>
+          <t>18/01/2023</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>9</v>
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J45" t="n">
         <v>14</v>
@@ -2905,19 +2905,19 @@
         <v>15</v>
       </c>
       <c r="L45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q45" t="n">
         <v>24</v>
@@ -2925,103 +2925,103 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18/01/2023</t>
+          <t>19/01/2023</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
         <v>15</v>
       </c>
       <c r="L46" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M46" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19/01/2023</t>
+          <t>20/01/2023</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O47" t="n">
         <v>22</v>
@@ -3030,16 +3030,16 @@
         <v>23</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20/01/2023</t>
+          <t>21/01/2023</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3055,19 +3055,19 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L48" t="n">
         <v>15</v>
@@ -3079,120 +3079,120 @@
         <v>19</v>
       </c>
       <c r="O48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21/01/2023</t>
+          <t>23/01/2023</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N49" t="n">
         <v>19</v>
       </c>
       <c r="O49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>23/01/2023</t>
+          <t>24/01/2023</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P50" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q50" t="n">
         <v>25</v>
@@ -3200,11 +3200,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24/01/2023</t>
+          <t>25/01/2023</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3217,80 +3217,80 @@
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
         <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25/01/2023</t>
+          <t>26/01/2023</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M52" t="n">
         <v>20</v>
@@ -3302,139 +3302,139 @@
         <v>22</v>
       </c>
       <c r="P52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>26/01/2023</t>
+          <t>27/01/2023</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L53" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O53" t="n">
         <v>22</v>
       </c>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>27/01/2023</t>
+          <t>28/01/2023</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L54" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M54" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N54" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>28/01/2023</t>
+          <t>30/01/2023</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
@@ -3449,25 +3449,25 @@
         <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
         <v>23</v>
@@ -3475,82 +3475,82 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30/01/2023</t>
+          <t>31/01/2023</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
         <v>13</v>
       </c>
       <c r="L56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P56" t="n">
         <v>20</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31/01/2023</t>
+          <t>01/02/2023</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
         <v>9</v>
@@ -3559,7 +3559,7 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
         <v>13</v>
@@ -3568,28 +3568,28 @@
         <v>14</v>
       </c>
       <c r="M57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N57" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O57" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01/02/2023</t>
+          <t>02/02/2023</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3599,40 +3599,40 @@
         <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O58" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P58" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -3640,54 +3640,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02/02/2023</t>
+          <t>03/02/2023</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
         <v>7</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J59" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O59" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q59" t="n">
         <v>25</v>
@@ -3695,39 +3695,39 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>03/02/2023</t>
+          <t>04/02/2023</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I60" t="n">
         <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L60" t="n">
         <v>18</v>
@@ -3742,7 +3742,7 @@
         <v>21</v>
       </c>
       <c r="P60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="n">
         <v>25</v>
@@ -3750,51 +3750,51 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>04/02/2023</t>
+          <t>06/02/2023</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>6</v>
       </c>
       <c r="G61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M61" t="n">
         <v>19</v>
       </c>
       <c r="N61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P61" t="n">
         <v>24</v>
@@ -3805,11 +3805,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>06/02/2023</t>
+          <t>07/02/2023</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3819,83 +3819,83 @@
         <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N62" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>07/02/2023</t>
+          <t>08/02/2023</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M63" t="n">
         <v>17</v>
@@ -3907,56 +3907,56 @@
         <v>21</v>
       </c>
       <c r="P63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>08/02/2023</t>
+          <t>09/02/2023</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I64" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J64" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O64" t="n">
         <v>21</v>
@@ -3965,41 +3965,41 @@
         <v>23</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09/02/2023</t>
+          <t>10/02/2023</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I65" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
         <v>17</v>
@@ -4014,10 +4014,10 @@
         <v>20</v>
       </c>
       <c r="O65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q65" t="n">
         <v>25</v>
@@ -4025,42 +4025,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/02/2023</t>
+          <t>11/02/2023</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I66" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J66" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L66" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M66" t="n">
         <v>19</v>
@@ -4069,7 +4069,7 @@
         <v>20</v>
       </c>
       <c r="O66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P66" t="n">
         <v>24</v>
@@ -4080,54 +4080,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/02/2023</t>
+          <t>13/02/2023</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M67" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q67" t="n">
         <v>25</v>
@@ -4135,121 +4135,121 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13/02/2023</t>
+          <t>14/02/2023</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M68" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N68" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O68" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P68" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14/02/2023</t>
+          <t>15/02/2023</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L69" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N69" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O69" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P69" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15/02/2023</t>
+          <t>16/02/2023</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4265,199 +4265,199 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J70" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K70" t="n">
         <v>13</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M70" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N70" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O70" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16/02/2023</t>
+          <t>17/02/2023</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I71" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J71" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K71" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L71" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M71" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N71" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O71" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17/02/2023</t>
+          <t>18/02/2023</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K72" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L72" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M72" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N72" t="n">
         <v>20</v>
       </c>
       <c r="O72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P72" t="n">
         <v>23</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18/02/2023</t>
+          <t>22/02/2023</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J73" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M73" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N73" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q73" t="n">
         <v>25</v>
@@ -4465,48 +4465,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22/02/2023</t>
+          <t>23/02/2023</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L74" t="n">
         <v>17</v>
       </c>
       <c r="M74" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N74" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O74" t="n">
         <v>23</v>
@@ -4520,27 +4520,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23/02/2023</t>
+          <t>24/02/2023</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H75" t="n">
         <v>10</v>
@@ -4552,7 +4552,7 @@
         <v>12</v>
       </c>
       <c r="K75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L75" t="n">
         <v>17</v>
@@ -4564,10 +4564,10 @@
         <v>19</v>
       </c>
       <c r="O75" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q75" t="n">
         <v>25</v>
@@ -4575,11 +4575,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24/02/2023</t>
+          <t>25/02/2023</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4589,95 +4589,95 @@
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I76" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J76" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L76" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M76" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N76" t="n">
         <v>19</v>
       </c>
       <c r="O76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P76" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25/02/2023</t>
+          <t>27/02/2023</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L77" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M77" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P77" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q77" t="n">
         <v>24</v>
@@ -4685,18 +4685,18 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>27/02/2023</t>
+          <t>28/02/2023</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>6</v>
@@ -4705,13 +4705,13 @@
         <v>7</v>
       </c>
       <c r="G78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J78" t="n">
         <v>13</v>
@@ -4723,10 +4723,10 @@
         <v>16</v>
       </c>
       <c r="M78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N78" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O78" t="n">
         <v>21</v>
@@ -4735,16 +4735,16 @@
         <v>22</v>
       </c>
       <c r="Q78" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28/02/2023</t>
+          <t>01/03/2023</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4754,25 +4754,25 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J79" t="n">
         <v>13</v>
       </c>
       <c r="K79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L79" t="n">
         <v>16</v>
@@ -4781,68 +4781,68 @@
         <v>17</v>
       </c>
       <c r="N79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q79" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01/03/2023</t>
+          <t>02/03/2023</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I80" t="n">
         <v>12</v>
       </c>
       <c r="J80" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M80" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N80" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O80" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P80" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q80" t="n">
         <v>25</v>
@@ -4850,42 +4850,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02/03/2023</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M81" t="n">
         <v>20</v>
@@ -4897,7 +4897,7 @@
         <v>22</v>
       </c>
       <c r="P81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q81" t="n">
         <v>25</v>
@@ -4905,51 +4905,51 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>04/03/2023</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L82" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N82" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O82" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P82" t="n">
         <v>24</v>
@@ -4960,103 +4960,103 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>04/03/2023</t>
+          <t>06/03/2023</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
         <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I83" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L83" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N83" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P83" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q83" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>06/03/2023</t>
+          <t>07/03/2023</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>8</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K84" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L84" t="n">
         <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N84" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O84" t="n">
         <v>21</v>
@@ -5070,18 +5070,18 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>07/03/2023</t>
+          <t>08/03/2023</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>5</v>
@@ -5090,211 +5090,211 @@
         <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N85" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O85" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>08/03/2023</t>
+          <t>09/03/2023</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G86" t="n">
         <v>7</v>
       </c>
       <c r="H86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I86" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L86" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O86" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P86" t="n">
         <v>23</v>
       </c>
       <c r="Q86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>09/03/2023</t>
+          <t>10/03/2023</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K87" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M87" t="n">
         <v>18</v>
       </c>
       <c r="N87" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O87" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P87" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10/03/2023</t>
+          <t>11/03/2023</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
       </c>
       <c r="K88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L88" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M88" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O88" t="n">
         <v>20</v>
       </c>
       <c r="P88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11/03/2023</t>
+          <t>13/03/2023</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -5304,162 +5304,162 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I89" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O89" t="n">
         <v>20</v>
       </c>
       <c r="P89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q89" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13/03/2023</t>
+          <t>14/03/2023</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H90" t="n">
         <v>11</v>
       </c>
       <c r="I90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L90" t="n">
         <v>17</v>
       </c>
       <c r="M90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N90" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O90" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q90" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14/03/2023</t>
+          <t>15/03/2023</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L91" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M91" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N91" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O91" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P91" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q91" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15/03/2023</t>
+          <t>16/03/2023</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5472,86 +5472,86 @@
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K92" t="n">
         <v>13</v>
       </c>
       <c r="L92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M92" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O92" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P92" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q92" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16/03/2023</t>
+          <t>17/03/2023</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
         <v>7</v>
       </c>
       <c r="H93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I93" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J93" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K93" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L93" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O93" t="n">
         <v>23</v>
@@ -5565,54 +5565,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17/03/2023</t>
+          <t>18/03/2023</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>6</v>
       </c>
       <c r="G94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I94" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K94" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L94" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N94" t="n">
         <v>21</v>
       </c>
       <c r="O94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q94" t="n">
         <v>25</v>
@@ -5620,97 +5620,97 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>18/03/2023</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G95" t="n">
         <v>8</v>
       </c>
       <c r="H95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I95" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K95" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M95" t="n">
         <v>19</v>
       </c>
       <c r="N95" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P95" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>21/03/2023</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F96" t="n">
         <v>7</v>
       </c>
       <c r="G96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H96" t="n">
         <v>11</v>
       </c>
       <c r="I96" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J96" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K96" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L96" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M96" t="n">
         <v>19</v>
@@ -5719,65 +5719,65 @@
         <v>20</v>
       </c>
       <c r="O96" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>22/03/2023</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L97" t="n">
         <v>16</v>
       </c>
       <c r="M97" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N97" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O97" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q97" t="n">
         <v>25</v>
@@ -5785,164 +5785,164 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>22/03/2023</t>
+          <t>23/03/2023</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O98" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P98" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q98" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23/03/2023</t>
+          <t>24/03/2023</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H99" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I99" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J99" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K99" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O99" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P99" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q99" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24/03/2023</t>
+          <t>25/03/2023</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H100" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L100" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q100" t="n">
         <v>25</v>
@@ -5950,11 +5950,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>25/03/2023</t>
+          <t>27/03/2023</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -5964,52 +5964,52 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H101" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J101" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L101" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M101" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N101" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O101" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>27/03/2023</t>
+          <t>28/03/2023</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6019,52 +6019,52 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H102" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I102" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K102" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L102" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O102" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
+          <t>29/03/2023</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6074,10 +6074,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G103" t="n">
         <v>8</v>
@@ -6086,7 +6086,7 @@
         <v>12</v>
       </c>
       <c r="I103" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J103" t="n">
         <v>15</v>
@@ -6095,10 +6095,10 @@
         <v>18</v>
       </c>
       <c r="L103" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M103" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N103" t="n">
         <v>22</v>
@@ -6115,11 +6115,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>29/03/2023</t>
+          <t>30/03/2023</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6129,10 +6129,10 @@
         <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
         <v>8</v>
@@ -6141,138 +6141,138 @@
         <v>12</v>
       </c>
       <c r="I104" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K104" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L104" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M104" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N104" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O104" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P104" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q104" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30/03/2023</t>
+          <t>31/03/2023</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L105" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M105" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P105" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q105" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>31/03/2023</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G106" t="n">
         <v>9</v>
       </c>
       <c r="H106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L106" t="n">
         <v>15</v>
       </c>
       <c r="M106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N106" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O106" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P106" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q106" t="n">
         <v>25</v>
@@ -6280,39 +6280,39 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L107" t="n">
         <v>15</v>
@@ -6321,13 +6321,13 @@
         <v>18</v>
       </c>
       <c r="N107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O107" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q107" t="n">
         <v>25</v>
@@ -6335,66 +6335,66 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>03/04/2023</t>
+          <t>04/04/2023</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J108" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K108" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L108" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M108" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N108" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P108" t="n">
         <v>23</v>
       </c>
       <c r="Q108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>04/04/2023</t>
+          <t>05/04/2023</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6404,205 +6404,205 @@
         <v>4</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G109" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L109" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M109" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N109" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P109" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q109" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>05/04/2023</t>
+          <t>06/04/2023</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I110" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M110" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N110" t="n">
         <v>20</v>
       </c>
       <c r="O110" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P110" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>06/04/2023</t>
+          <t>08/04/2023</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>4</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I111" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J111" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K111" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O111" t="n">
         <v>22</v>
       </c>
       <c r="P111" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q111" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>08/04/2023</t>
+          <t>10/04/2023</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G112" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I112" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J112" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K112" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L112" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N112" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P112" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q112" t="n">
         <v>25</v>
@@ -55445,6 +55445,61 @@
         <v>24</v>
       </c>
       <c r="Q1000" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>12</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1001" t="n">
+        <v>16</v>
+      </c>
+      <c r="L1001" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1001" t="n">
+        <v>19</v>
+      </c>
+      <c r="N1001" t="n">
+        <v>20</v>
+      </c>
+      <c r="O1001" t="n">
+        <v>21</v>
+      </c>
+      <c r="P1001" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q1001" t="n">
         <v>25</v>
       </c>
     </row>

--- a/base/base_limpa.xlsx
+++ b/base/base_limpa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:Q1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,121 +505,121 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13/03/2023</t>
+          <t>14/03/2023</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
         <v>17</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14/03/2023</t>
+          <t>15/03/2023</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
         <v>16</v>
       </c>
-      <c r="L3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M3" t="n">
-        <v>19</v>
-      </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15/03/2023</t>
+          <t>16/03/2023</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -632,86 +632,86 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16/03/2023</t>
+          <t>17/03/2023</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
         <v>23</v>
@@ -725,54 +725,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/03/2023</t>
+          <t>18/03/2023</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
         <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>25</v>
@@ -780,98 +780,98 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18/03/2023</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" t="n">
         <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>21/03/2023</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" t="n">
         <v>16</v>
       </c>
-      <c r="K8" t="n">
-        <v>17</v>
-      </c>
-      <c r="L8" t="n">
-        <v>18</v>
-      </c>
       <c r="M8" t="n">
         <v>19</v>
       </c>
@@ -879,65 +879,65 @@
         <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>22/03/2023</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
@@ -945,164 +945,164 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/03/2023</t>
+          <t>23/03/2023</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/03/2023</t>
+          <t>24/03/2023</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24/03/2023</t>
+          <t>25/03/2023</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" t="n">
         <v>16</v>
       </c>
-      <c r="K12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L12" t="n">
-        <v>18</v>
-      </c>
       <c r="M12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
         <v>25</v>
@@ -1110,11 +1110,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25/03/2023</t>
+          <t>27/03/2023</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1124,52 +1124,52 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27/03/2023</t>
+          <t>28/03/2023</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1179,52 +1179,52 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
+          <t>29/03/2023</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1234,10 +1234,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>8</v>
@@ -1246,7 +1246,7 @@
         <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
         <v>15</v>
@@ -1255,10 +1255,10 @@
         <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>22</v>
@@ -1275,11 +1275,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29/03/2023</t>
+          <t>30/03/2023</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1289,10 +1289,10 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>8</v>
@@ -1301,138 +1301,138 @@
         <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30/03/2023</t>
+          <t>31/03/2023</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31/03/2023</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
         <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
         <v>25</v>
@@ -1440,39 +1440,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
         <v>15</v>
@@ -1481,13 +1481,13 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" t="n">
         <v>25</v>
@@ -1495,66 +1495,66 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03/04/2023</t>
+          <t>04/04/2023</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" t="n">
         <v>23</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/04/2023</t>
+          <t>05/04/2023</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1564,205 +1564,205 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/04/2023</t>
+          <t>06/04/2023</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
         <v>20</v>
       </c>
       <c r="O22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06/04/2023</t>
+          <t>08/04/2023</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O23" t="n">
         <v>22</v>
       </c>
       <c r="P23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>08/04/2023</t>
+          <t>10/04/2023</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q24" t="n">
         <v>25</v>
@@ -1770,54 +1770,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/04/2023</t>
+          <t>11/04/2023</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q25" t="n">
         <v>25</v>
@@ -1825,54 +1825,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11/04/2023</t>
+          <t>12/04/2023</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
         <v>25</v>
@@ -1880,54 +1880,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12/04/2023</t>
+          <t>13/04/2023</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M27" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q27" t="n">
         <v>25</v>
@@ -1935,51 +1935,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13/04/2023</t>
+          <t>14/04/2023</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M28" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
         <v>24</v>
@@ -1990,39 +1990,39 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14/04/2023</t>
+          <t>15/04/2023</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
@@ -2031,13 +2031,13 @@
         <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q29" t="n">
         <v>25</v>
@@ -2045,21 +2045,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15/04/2023</t>
+          <t>17/04/2023</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -2074,25 +2074,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q30" t="n">
         <v>25</v>
@@ -2100,54 +2100,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17/04/2023</t>
+          <t>18/04/2023</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q31" t="n">
         <v>25</v>
@@ -2155,18 +2155,18 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18/04/2023</t>
+          <t>19/04/2023</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>6</v>
@@ -2175,16 +2175,16 @@
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
         <v>16</v>
@@ -2193,16 +2193,16 @@
         <v>17</v>
       </c>
       <c r="M32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q32" t="n">
         <v>25</v>
@@ -2210,42 +2210,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19/04/2023</t>
+          <t>20/04/2023</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
         <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M33" t="n">
         <v>18</v>
@@ -2257,29 +2257,29 @@
         <v>21</v>
       </c>
       <c r="P33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20/04/2023</t>
+          <t>22/04/2023</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -2288,22 +2288,22 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
         <v>20</v>
@@ -2315,16 +2315,16 @@
         <v>22</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22/04/2023</t>
+          <t>24/04/2023</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2337,34 +2337,34 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L35" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P35" t="n">
         <v>22</v>
@@ -2375,54 +2375,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24/04/2023</t>
+          <t>25/04/2023</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L36" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O36" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="n">
         <v>25</v>
@@ -2430,54 +2430,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>25/04/2023</t>
+          <t>26/04/2023</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
         <v>16</v>
       </c>
       <c r="L37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O37" t="n">
         <v>22</v>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q37" t="n">
         <v>25</v>
@@ -2485,45 +2485,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>26/04/2023</t>
+          <t>27/04/2023</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J38" t="n">
         <v>14</v>
       </c>
       <c r="K38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" t="n">
         <v>16</v>
       </c>
-      <c r="L38" t="n">
-        <v>18</v>
-      </c>
       <c r="M38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N38" t="n">
         <v>20</v>
@@ -2535,38 +2535,38 @@
         <v>23</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27/04/2023</t>
+          <t>28/04/2023</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J39" t="n">
         <v>14</v>
@@ -2584,41 +2584,41 @@
         <v>20</v>
       </c>
       <c r="O39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2799</v>
+        <v>2800</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>28/04/2023</t>
+          <t>29/04/2023</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
         <v>13</v>
@@ -2633,7 +2633,7 @@
         <v>16</v>
       </c>
       <c r="M40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
         <v>20</v>
@@ -2650,66 +2650,66 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2800</v>
+        <v>2801</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>29/04/2023</t>
+          <t>02/05/2023</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N41" t="n">
         <v>20</v>
       </c>
       <c r="O41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02/05/2023</t>
+          <t>03/05/2023</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2722,37 +2722,37 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K42" t="n">
+        <v>13</v>
+      </c>
+      <c r="L42" t="n">
         <v>16</v>
       </c>
-      <c r="K42" t="n">
-        <v>17</v>
-      </c>
-      <c r="L42" t="n">
-        <v>18</v>
-      </c>
       <c r="M42" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O42" t="n">
         <v>22</v>
       </c>
       <c r="P42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q42" t="n">
         <v>25</v>
@@ -2760,54 +2760,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2802</v>
+        <v>2803</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03/05/2023</t>
+          <t>04/05/2023</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L43" t="n">
         <v>16</v>
       </c>
       <c r="M43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
         <v>25</v>
@@ -2815,21 +2815,21 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/05/2023</t>
+          <t>05/05/2023</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
         <v>7</v>
@@ -2841,111 +2841,111 @@
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L44" t="n">
+        <v>13</v>
+      </c>
+      <c r="M44" t="n">
+        <v>14</v>
+      </c>
+      <c r="N44" t="n">
         <v>16</v>
       </c>
-      <c r="M44" t="n">
-        <v>18</v>
-      </c>
-      <c r="N44" t="n">
-        <v>20</v>
-      </c>
       <c r="O44" t="n">
         <v>21</v>
       </c>
       <c r="P44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>05/05/2023</t>
+          <t>06/05/2023</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L45" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M45" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P45" t="n">
         <v>23</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>06/05/2023</t>
+          <t>08/05/2023</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
         <v>11</v>
@@ -2960,16 +2960,16 @@
         <v>14</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M46" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P46" t="n">
         <v>23</v>
@@ -2980,106 +2980,106 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>08/05/2023</t>
+          <t>09/05/2023</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L47" t="n">
+        <v>13</v>
+      </c>
+      <c r="M47" t="n">
+        <v>14</v>
+      </c>
+      <c r="N47" t="n">
+        <v>15</v>
+      </c>
+      <c r="O47" t="n">
         <v>16</v>
       </c>
-      <c r="M47" t="n">
-        <v>17</v>
-      </c>
-      <c r="N47" t="n">
-        <v>19</v>
-      </c>
-      <c r="O47" t="n">
-        <v>20</v>
-      </c>
       <c r="P47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09/05/2023</t>
+          <t>10/05/2023</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J48" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L48" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M48" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O48" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P48" t="n">
         <v>22</v>
@@ -3090,106 +3090,106 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/05/2023</t>
+          <t>11/05/2023</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I49" t="n">
         <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/05/2023</t>
+          <t>12/05/2023</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P50" t="n">
         <v>24</v>
@@ -3200,54 +3200,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/05/2023</t>
+          <t>13/05/2023</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M51" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N51" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="n">
         <v>25</v>
@@ -3255,54 +3255,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13/05/2023</t>
+          <t>15/05/2023</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L52" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M52" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N52" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q52" t="n">
         <v>25</v>
@@ -3310,51 +3310,51 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15/05/2023</t>
+          <t>16/05/2023</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M53" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P53" t="n">
         <v>24</v>
@@ -3365,11 +3365,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16/05/2023</t>
+          <t>17/05/2023</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3379,37 +3379,37 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H54" t="n">
         <v>11</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K54" t="n">
         <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P54" t="n">
         <v>24</v>
@@ -3420,51 +3420,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17/05/2023</t>
+          <t>18/05/2023</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N55" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P55" t="n">
         <v>24</v>
@@ -3475,48 +3475,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18/05/2023</t>
+          <t>19/05/2023</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O56" t="n">
         <v>22</v>
@@ -3530,45 +3530,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19/05/2023</t>
+          <t>20/05/2023</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J57" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
         <v>21</v>
@@ -3585,66 +3585,66 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20/05/2023</t>
+          <t>22/05/2023</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L58" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M58" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N58" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O58" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P58" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22/05/2023</t>
+          <t>23/05/2023</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3654,40 +3654,40 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M59" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N59" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O59" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P59" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q59" t="n">
         <v>24</v>
@@ -3695,97 +3695,97 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23/05/2023</t>
+          <t>24/05/2023</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H60" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J60" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K60" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L60" t="n">
         <v>18</v>
       </c>
       <c r="M60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P60" t="n">
         <v>23</v>
       </c>
       <c r="Q60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24/05/2023</t>
+          <t>25/05/2023</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M61" t="n">
         <v>19</v>
@@ -3797,10 +3797,10 @@
         <v>21</v>
       </c>
       <c r="P61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -55445,6 +55445,61 @@
         <v>24</v>
       </c>
       <c r="Q1000" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>3761</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>13</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>14</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1001" t="n">
+        <v>16</v>
+      </c>
+      <c r="L1001" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1001" t="n">
+        <v>18</v>
+      </c>
+      <c r="N1001" t="n">
+        <v>21</v>
+      </c>
+      <c r="O1001" t="n">
+        <v>23</v>
+      </c>
+      <c r="P1001" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q1001" t="n">
         <v>25</v>
       </c>
     </row>

--- a/base/base_limpa.xlsx
+++ b/base/base_limpa.xlsx
@@ -39335,36 +39335,36 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>13/09/2025</t>
         </is>
       </c>
       <c r="C708" t="n">
         <v>2</v>
       </c>
       <c r="D708" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E708" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F708" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G708" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H708" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I708" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J708" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K708" t="n">
         <v>16</v>
@@ -39379,120 +39379,120 @@
         <v>19</v>
       </c>
       <c r="O708" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P708" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q708" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D709" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E709" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F709" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G709" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H709" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I709" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J709" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K709" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L709" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M709" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N709" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O709" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P709" t="n">
         <v>22</v>
       </c>
       <c r="Q709" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="C710" t="n">
         <v>1</v>
       </c>
       <c r="D710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E710" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F710" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G710" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H710" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I710" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J710" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K710" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L710" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M710" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N710" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O710" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P710" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q710" t="n">
         <v>25</v>
@@ -39500,54 +39500,54 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D711" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E711" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F711" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G711" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H711" t="n">
         <v>11</v>
       </c>
       <c r="I711" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J711" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K711" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L711" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M711" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N711" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O711" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P711" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q711" t="n">
         <v>25</v>
@@ -39555,54 +39555,54 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D712" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E712" t="n">
         <v>4</v>
       </c>
       <c r="F712" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G712" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H712" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I712" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J712" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K712" t="n">
         <v>15</v>
       </c>
       <c r="L712" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M712" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N712" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O712" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P712" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q712" t="n">
         <v>25</v>
@@ -39610,18 +39610,18 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D713" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E713" t="n">
         <v>4</v>
@@ -39636,28 +39636,28 @@
         <v>10</v>
       </c>
       <c r="I713" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J713" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K713" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L713" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M713" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N713" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O713" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P713" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q713" t="n">
         <v>25</v>
@@ -39665,11 +39665,11 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>20/09/2025</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -39682,126 +39682,126 @@
         <v>4</v>
       </c>
       <c r="F714" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G714" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H714" t="n">
         <v>10</v>
       </c>
       <c r="I714" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J714" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K714" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L714" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M714" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N714" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O714" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P714" t="n">
         <v>23</v>
       </c>
       <c r="Q714" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>22/09/2025</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D715" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E715" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F715" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G715" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H715" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I715" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J715" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K715" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L715" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M715" t="n">
         <v>19</v>
       </c>
       <c r="N715" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O715" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P715" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q715" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E716" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F716" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G716" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H716" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I716" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J716" t="n">
         <v>15</v>
@@ -39810,19 +39810,19 @@
         <v>16</v>
       </c>
       <c r="L716" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M716" t="n">
         <v>19</v>
       </c>
       <c r="N716" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O716" t="n">
         <v>22</v>
       </c>
       <c r="P716" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q716" t="n">
         <v>25</v>
@@ -39830,21 +39830,21 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D717" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E717" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F717" t="n">
         <v>8</v>
@@ -39856,95 +39856,95 @@
         <v>11</v>
       </c>
       <c r="I717" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J717" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K717" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L717" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M717" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N717" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O717" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P717" t="n">
         <v>23</v>
       </c>
       <c r="Q717" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="C718" t="n">
         <v>1</v>
       </c>
       <c r="D718" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E718" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F718" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G718" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H718" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I718" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J718" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K718" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L718" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M718" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N718" t="n">
         <v>18</v>
       </c>
       <c r="O718" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P718" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q718" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>27/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -39960,233 +39960,233 @@
         <v>4</v>
       </c>
       <c r="G719" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H719" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I719" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J719" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K719" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L719" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M719" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N719" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O719" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P719" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q719" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>27/09/2025</t>
         </is>
       </c>
       <c r="C720" t="n">
         <v>1</v>
       </c>
       <c r="D720" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E720" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F720" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G720" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H720" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I720" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J720" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K720" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L720" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M720" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N720" t="n">
         <v>19</v>
       </c>
       <c r="O720" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P720" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q720" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="C721" t="n">
         <v>1</v>
       </c>
       <c r="D721" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E721" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F721" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G721" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H721" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I721" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J721" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K721" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L721" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M721" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N721" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O721" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P721" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q721" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="C722" t="n">
         <v>1</v>
       </c>
       <c r="D722" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E722" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F722" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G722" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H722" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I722" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J722" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K722" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L722" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M722" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N722" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O722" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P722" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q722" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D723" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E723" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F723" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G723" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H723" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I723" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J723" t="n">
         <v>15</v>
@@ -40195,38 +40195,38 @@
         <v>16</v>
       </c>
       <c r="L723" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M723" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N723" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O723" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P723" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q723" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D724" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E724" t="n">
         <v>6</v>
@@ -40238,31 +40238,31 @@
         <v>8</v>
       </c>
       <c r="H724" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I724" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J724" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K724" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L724" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M724" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N724" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O724" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P724" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q724" t="n">
         <v>25</v>
@@ -40270,54 +40270,54 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="C725" t="n">
         <v>1</v>
       </c>
       <c r="D725" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E725" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F725" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G725" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H725" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I725" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J725" t="n">
         <v>12</v>
       </c>
       <c r="K725" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L725" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M725" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N725" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O725" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P725" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q725" t="n">
         <v>25</v>
@@ -40325,11 +40325,11 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -40339,37 +40339,37 @@
         <v>2</v>
       </c>
       <c r="E726" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F726" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G726" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H726" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I726" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J726" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K726" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L726" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M726" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N726" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O726" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P726" t="n">
         <v>23</v>
@@ -40380,54 +40380,54 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D727" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E727" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F727" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G727" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H727" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I727" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J727" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K727" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L727" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M727" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N727" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O727" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P727" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q727" t="n">
         <v>25</v>
@@ -40435,51 +40435,51 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D728" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E728" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F728" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G728" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H728" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I728" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J728" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K728" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L728" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M728" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N728" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O728" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P728" t="n">
         <v>24</v>
@@ -40490,15 +40490,15 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D729" t="n">
         <v>3</v>
@@ -40507,49 +40507,49 @@
         <v>4</v>
       </c>
       <c r="F729" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G729" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H729" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I729" t="n">
         <v>11</v>
       </c>
       <c r="J729" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K729" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L729" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M729" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N729" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O729" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P729" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q729" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -40562,129 +40562,129 @@
         <v>4</v>
       </c>
       <c r="F730" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G730" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H730" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I730" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J730" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K730" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L730" t="n">
         <v>16</v>
       </c>
       <c r="M730" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N730" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O730" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P730" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q730" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="C731" t="n">
         <v>1</v>
       </c>
       <c r="D731" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E731" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F731" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G731" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H731" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I731" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J731" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K731" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L731" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M731" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N731" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O731" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P731" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q731" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D732" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E732" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F732" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G732" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H732" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I732" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J732" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K732" t="n">
         <v>13</v>
@@ -40696,44 +40696,44 @@
         <v>15</v>
       </c>
       <c r="N732" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O732" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P732" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q732" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D733" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E733" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F733" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G733" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H733" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I733" t="n">
         <v>9</v>
@@ -40751,120 +40751,120 @@
         <v>15</v>
       </c>
       <c r="N733" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O733" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P733" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q733" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D734" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E734" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F734" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G734" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H734" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I734" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J734" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K734" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L734" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M734" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N734" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O734" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P734" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q734" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D735" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E735" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F735" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G735" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H735" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I735" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J735" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K735" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L735" t="n">
         <v>16</v>
       </c>
       <c r="M735" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N735" t="n">
         <v>20</v>
       </c>
       <c r="O735" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P735" t="n">
         <v>23</v>
@@ -40875,48 +40875,48 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="C736" t="n">
         <v>1</v>
       </c>
       <c r="D736" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E736" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F736" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G736" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H736" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I736" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J736" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K736" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L736" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M736" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N736" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O736" t="n">
         <v>21</v>
@@ -40930,48 +40930,48 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D737" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E737" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F737" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G737" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H737" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I737" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J737" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K737" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L737" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M737" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N737" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O737" t="n">
         <v>21</v>
@@ -40980,41 +40980,41 @@
         <v>23</v>
       </c>
       <c r="Q737" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D738" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E738" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F738" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G738" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H738" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I738" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J738" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K738" t="n">
         <v>17</v>
@@ -41032,10 +41032,10 @@
         <v>21</v>
       </c>
       <c r="P738" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q738" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="739">
@@ -46155,54 +46155,54 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>3611</v>
+        <v>3612</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="C832" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D832" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E832" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F832" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G832" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H832" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I832" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J832" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K832" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L832" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M832" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N832" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O832" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P832" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q832" t="n">
         <v>25</v>
